--- a/automation/stadtratsbeschluesse/SKZ_Beschluesse_Metadaten.xlsx
+++ b/automation/stadtratsbeschluesse/SKZ_Beschluesse_Metadaten.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sszgua\Python\git\opendatazurich.github.io\automation\stadtratsbeschluesse\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sszgua\git\opendatazurich.github.io\automation\stadtratsbeschluesse\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E16CFA22-E7C7-4ED0-ABCF-334352EE3A8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC49BEC4-A632-4E62-95C0-240869CB06A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1500" yWindow="-120" windowWidth="27420" windowHeight="18240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="metadata" sheetId="14" r:id="rId1"/>
@@ -962,12 +962,6 @@
     <t>28.01.2025</t>
   </si>
   <si>
-    <t>Öffentliche Beschlüsse des Stadtrats der Stadt Zürich, seit 2025</t>
-  </si>
-  <si>
-    <t>18.02.2025 - heute</t>
-  </si>
-  <si>
     <t>Link</t>
   </si>
   <si>
@@ -1038,6 +1032,12 @@
   </si>
   <si>
     <t>politik, verwaltung</t>
+  </si>
+  <si>
+    <t>Öffentliche Beschlüsse des Stadtrats der Stadt Zürich, seit 2010</t>
+  </si>
+  <si>
+    <t>04.01.2010 - heute</t>
   </si>
 </sst>
 </file>
@@ -1951,7 +1951,7 @@
         <v>14</v>
       </c>
       <c r="D3" s="32" t="s">
-        <v>164</v>
+        <v>188</v>
       </c>
       <c r="E3" s="7"/>
       <c r="F3" s="35" t="s">
@@ -1969,7 +1969,7 @@
         <v>14</v>
       </c>
       <c r="D4" s="19" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="E4" s="7"/>
       <c r="F4" s="34" t="s">
@@ -2057,7 +2057,7 @@
         <v>14</v>
       </c>
       <c r="D9" s="32" t="s">
-        <v>165</v>
+        <v>189</v>
       </c>
       <c r="E9" s="7"/>
       <c r="F9" s="34" t="s">
@@ -2420,13 +2420,13 @@
         <v>30</v>
       </c>
       <c r="B34" s="19" t="s">
+        <v>164</v>
+      </c>
+      <c r="C34" s="19" t="s">
+        <v>165</v>
+      </c>
+      <c r="D34" s="19" t="s">
         <v>166</v>
-      </c>
-      <c r="C34" s="19" t="s">
-        <v>167</v>
-      </c>
-      <c r="D34" s="19" t="s">
-        <v>168</v>
       </c>
       <c r="E34" s="7"/>
       <c r="F34" s="36"/>
@@ -2557,7 +2557,7 @@
         <v>69</v>
       </c>
       <c r="B1" s="22" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="15" x14ac:dyDescent="0.2">
@@ -2565,7 +2565,7 @@
         <v>101</v>
       </c>
       <c r="B2" s="53" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="15" x14ac:dyDescent="0.2">
@@ -2573,7 +2573,7 @@
         <v>102</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="15" x14ac:dyDescent="0.2">
@@ -2581,7 +2581,7 @@
         <v>103</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="15" x14ac:dyDescent="0.2">
@@ -2589,7 +2589,7 @@
         <v>104</v>
       </c>
       <c r="B5" s="21" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="15" x14ac:dyDescent="0.2">
@@ -2597,7 +2597,7 @@
         <v>105</v>
       </c>
       <c r="B6" s="53" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="15" x14ac:dyDescent="0.2">
@@ -2605,7 +2605,7 @@
         <v>106</v>
       </c>
       <c r="B7" s="53" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="15" x14ac:dyDescent="0.2">
@@ -2613,7 +2613,7 @@
         <v>107</v>
       </c>
       <c r="B8" s="53" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="15" x14ac:dyDescent="0.2">
@@ -2621,7 +2621,7 @@
         <v>108</v>
       </c>
       <c r="B9" s="53" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="15" x14ac:dyDescent="0.2">
@@ -2629,7 +2629,7 @@
         <v>109</v>
       </c>
       <c r="B10" s="53" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="15" x14ac:dyDescent="0.2">
@@ -2637,7 +2637,7 @@
         <v>110</v>
       </c>
       <c r="B11" s="53" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="15" x14ac:dyDescent="0.2">
@@ -2645,7 +2645,7 @@
         <v>111</v>
       </c>
       <c r="B12" s="53" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="15" x14ac:dyDescent="0.2">
@@ -2653,7 +2653,7 @@
         <v>112</v>
       </c>
       <c r="B13" s="53" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="15" x14ac:dyDescent="0.2">
@@ -2661,7 +2661,7 @@
         <v>113</v>
       </c>
       <c r="B14" s="53" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="15" x14ac:dyDescent="0.2">
@@ -2669,7 +2669,7 @@
         <v>114</v>
       </c>
       <c r="B15" s="53" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="15" x14ac:dyDescent="0.2">
@@ -2677,7 +2677,7 @@
         <v>115</v>
       </c>
       <c r="B16" s="53" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="15" x14ac:dyDescent="0.2">
@@ -2685,7 +2685,7 @@
         <v>116</v>
       </c>
       <c r="B17" s="53" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="15" x14ac:dyDescent="0.2">
@@ -2693,7 +2693,7 @@
         <v>117</v>
       </c>
       <c r="B18" s="53" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="15" x14ac:dyDescent="0.2">
@@ -2701,7 +2701,7 @@
         <v>118</v>
       </c>
       <c r="B19" s="53" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="15" x14ac:dyDescent="0.2">
@@ -2709,7 +2709,7 @@
         <v>119</v>
       </c>
       <c r="B20" s="53" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
@@ -3281,6 +3281,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x0101008CBAF0EEED2F5B4AB4463B97C2AD2B71" ma:contentTypeVersion="0" ma:contentTypeDescription="Ein neues Dokument erstellen." ma:contentTypeScope="" ma:versionID="d2bc9691d179cb44d4ba77bdf8fcfb4a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="66c4a6dd5ef775a5269b08f7de37f93f">
     <xsd:element name="properties">
@@ -3394,22 +3409,30 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C6056489-A7A4-4445-AFC5-87E5586E5E93}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B4B3AD83-9986-4E71-995F-A94C1CED6EB8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F33FC2A8-E9AF-48AF-8CDC-2C0CCE48C45D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3423,27 +3446,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B4B3AD83-9986-4E71-995F-A94C1CED6EB8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C6056489-A7A4-4445-AFC5-87E5586E5E93}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>